--- a/reports/jobs_2026-08-26.xlsx
+++ b/reports/jobs_2026-08-26.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Errors" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I90"/>
+  <dimension ref="A1:I88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -968,7 +968,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Theorem Proving Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -981,7 +981,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -989,7 +993,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/austin/theorem-proving-engineer/33099/97584421536</t>
+          <t>https://careers.arm.com/job/bengaluru/engineer/33099/99657761504</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1006,17 +1010,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Arm India</t>
+          <t>Atlan</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Embedded Compiler Engineer (Machine Learning)</t>
+          <t>Field Security Engineer</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1024,7 +1028,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -1032,12 +1040,12 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/lund/embedded-compiler-engineer-machine-learning/33099/94847322016</t>
+          <t>https://jobs.ashbyhq.com/atlan/b2b880ed-63cd-4f56-8313-87f143fa9807</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/</t>
+          <t>https://jobs.ashbyhq.com/atlan</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1049,12 +1057,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Atlan</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Field Security Engineer</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1067,11 +1075,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
+      <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -1079,12 +1083,12 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/atlan/b2b880ed-63cd-4f56-8313-87f143fa9807</t>
+          <t>https://www.atlassian.com/company/careers/engineering</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/atlan</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1101,12 +1105,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>AI and Machine Learning</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1122,7 +1126,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/engineering</t>
+          <t>https://www.atlassian.com/company/careers/engineering/ai</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1139,17 +1143,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Cloudflare India</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>AI and Machine Learning</t>
+          <t>Customer Engineer, India (Based in Mumbai)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1157,7 +1161,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Remote India</t>
+        </is>
+      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -1165,12 +1173,12 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/engineering/ai</t>
+          <t>https://boards.greenhouse.io/cloudflare/jobs/7955378?gh_jid=7955378</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://boards.greenhouse.io/cloudflare</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1182,12 +1190,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Cloudflare India</t>
+          <t>Continental India</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Customer Engineer, India (Based in Mumbai)</t>
+          <t>Technical Service Engineer – RE</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1202,7 +1210,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Remote India</t>
+          <t>Faridabad, in</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1212,12 +1220,12 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/cloudflare/jobs/7955378?gh_jid=7955378</t>
+          <t>https://api.smartrecruiters.com/v1/companies/continental/postings/744000145441139</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/cloudflare</t>
+          <t>https://careers.smartrecruiters.com/continental</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1229,17 +1237,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Continental India</t>
+          <t>Databricks India</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Technical Service Engineer – RE</t>
+          <t>AI Engineer - FDE (Forward Deployed Engineer)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1249,7 +1257,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Faridabad, in</t>
+          <t>Remote - India</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1259,12 +1267,12 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/continental/postings/744000145441139</t>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8099751002</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/continental</t>
+          <t>https://boards.greenhouse.io/databricks</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1276,17 +1284,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Databricks India</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>AI Engineer - FDE (Forward Deployed Engineer)</t>
+          <t>Implementation Engineer</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1296,7 +1304,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Remote - India</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1306,12 +1314,12 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8099751002</t>
+          <t>https://exotel.com/about-us/careers/#op-575251-implementation-engineer</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/databricks</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1343,7 +1351,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Gurgaon Full-time</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1353,7 +1361,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-575251-implementation-engineer</t>
+          <t>https://exotel.com/about-us/careers/#op-689879-implementation-engineer-</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1375,12 +1383,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Implementation Engineer</t>
+          <t>Integration &amp; Customisation Engineer (PHP + React.JS)</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1390,7 +1398,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Gurgaon Full-time</t>
+          <t>India Full-time</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1400,7 +1408,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-689879-implementation-engineer-</t>
+          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-php--reactjs</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1422,7 +1430,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer (PHP + React.JS)</t>
+          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1435,11 +1443,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>India Full-time</t>
-        </is>
-      </c>
+      <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -1447,7 +1451,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-php--reactjs</t>
+          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1469,12 +1473,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
+          <t>Tech Support Intern</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1482,7 +1486,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr"/>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -1490,7 +1498,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
+          <t>https://exotel.com/about-us/careers/#op-698555-tech-support-intern</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1512,7 +1520,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Tech Support Intern</t>
+          <t>Product Support Intern (API Integration)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1537,7 +1545,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-698555-tech-support-intern</t>
+          <t>https://exotel.com/about-us/careers/#op-685404-product-support-intern-api-integration</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1559,12 +1567,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Product Support Intern (API Integration)</t>
+          <t>Software Engineer - 3 (Voice)</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1584,7 +1592,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-685404-product-support-intern-api-integration</t>
+          <t>https://exotel.com/about-us/careers/#op-704555-software-engineer-3-voice</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1606,12 +1614,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer - 3 (Voice)</t>
+          <t>Software Engineer 3 (Full Stack)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1631,7 +1639,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704555-software-engineer-3-voice</t>
+          <t>https://exotel.com/about-us/careers/#op-697293-software-engineer-3-full-stack</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1653,12 +1661,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer 3 (Full Stack)</t>
+          <t>Integration &amp; Customization Engineer -1</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1668,7 +1676,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>India Full-time</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1678,7 +1686,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-697293-software-engineer-3-full-stack</t>
+          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1700,7 +1708,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Integration &amp; Customization Engineer -1</t>
+          <t>Integration &amp; Customisation Engineer-1 (Chatbot)</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1715,7 +1723,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>India Full-time</t>
+          <t>Bengaluru Full-time</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1725,7 +1733,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
+          <t>https://exotel.com/about-us/careers/#op-638792-integration--customisation-engineer1-chatbot</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1747,12 +1755,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer-1 (Chatbot)</t>
+          <t>Software Developer - 3 (Golang/Java/Python)</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1762,7 +1770,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru Full-time</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1772,7 +1780,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-638792-integration--customisation-engineer1-chatbot</t>
+          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-golangjavapython</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1794,12 +1802,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Software Developer - 3 (Golang/Java/Python)</t>
+          <t>Software Engineer - 2 (Voicebot)</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1819,7 +1827,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-golangjavapython</t>
+          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1841,7 +1849,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer - 2 (Voicebot)</t>
+          <t>Software Engineer - 3 (Gen AI &amp; Speech)</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1856,7 +1864,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bangalore Full-time</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1866,7 +1874,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
+          <t>https://exotel.com/about-us/careers/#op-694350-software-engineer-3-gen-ai--speech</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1888,12 +1896,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer - 3 (Gen AI &amp; Speech)</t>
+          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1903,7 +1911,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Bangalore Full-time</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1913,7 +1921,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-694350-software-engineer-3-gen-ai--speech</t>
+          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1930,17 +1938,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Fi Money</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
+          <t>Ai Engg Intern</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1950,7 +1958,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1960,12 +1968,12 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
+          <t>https://jobs.lever.co/epifi/08c743e8-2b29-4f78-827e-5bd90476ed86</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://jobs.lever.co/epifi</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -1982,7 +1990,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Ai Engg Intern</t>
+          <t>DS/ML Intern</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2007,7 +2015,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08c743e8-2b29-4f78-827e-5bd90476ed86</t>
+          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2029,7 +2037,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>DS/ML Intern</t>
+          <t>GenAI Product Builder Intern</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2054,7 +2062,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
+          <t>https://jobs.lever.co/epifi/4f5b7548-ea0a-4be0-816b-11d712853169</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2071,17 +2079,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Fi Money</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>GenAI Product Builder Intern</t>
+          <t>UI Developer - Digital Products</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2089,11 +2097,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -2101,12 +2105,12 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/4f5b7548-ea0a-4be0-816b-11d712853169</t>
+          <t>https://fractal.ai/en-US/Careers/job/Texas/UI-Developer---Digital-Products_SR-45168-1</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2123,7 +2127,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>UI Developer - Digital Products</t>
+          <t>Snowflake_DBT Developers</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2144,7 +2148,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Texas/UI-Developer---Digital-Products_SR-45168-1</t>
+          <t>https://fractal.ai/en-US/Careers/job/New-York/Snowflake-DBT-Developers_SR-44592-1</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2166,12 +2170,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Snowflake_DBT Developers</t>
+          <t>Full Stack Developer Role (Java + React)</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2187,7 +2191,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/New-York/Snowflake-DBT-Developers_SR-44592-1</t>
+          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/Full-Stack-Developer-Role--Java---React-_SR-38370-1</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2209,12 +2213,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Full Stack Developer Role (Java + React)</t>
+          <t>SAP BW HANA Developer</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2230,7 +2234,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/Full-Stack-Developer-Role--Java---React-_SR-38370-1</t>
+          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/SAP-BW-HANA-Developer_SR-43859</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2247,17 +2251,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Freshworks</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>SAP BW HANA Developer</t>
+          <t>Specialist - Data Platform Engineering</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2265,7 +2269,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Chennai, in</t>
+        </is>
+      </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -2273,12 +2281,12 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/SAP-BW-HANA-Developer_SR-43859</t>
+          <t>https://api.smartrecruiters.com/v1/companies/Freshworks/postings/744000143102264</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://careers.smartrecruiters.com/Freshworks</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -2290,17 +2298,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Freshworks</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Specialist - Data Platform Engineering</t>
+          <t>Internships and Programs</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2308,11 +2316,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>Chennai, in</t>
-        </is>
-      </c>
+      <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="2" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -2320,12 +2324,12 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/Freshworks/postings/744000143102264</t>
+          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/Freshworks</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -2342,12 +2346,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Internships and Programs</t>
+          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2363,7 +2367,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
+          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2380,12 +2384,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>HighRadius</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2398,7 +2402,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana, India</t>
+        </is>
+      </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -2406,12 +2414,12 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
+          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://boards.greenhouse.io/highradius</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -2423,12 +2431,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>HighRadius</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2443,7 +2451,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>New Delhi, in</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -2453,12 +2461,12 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/highradius</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2475,12 +2483,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
+          <t>Machine Learning Engineer (Agent Intelligence &amp; Evaluations)</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2500,7 +2508,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000143976319</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2522,12 +2530,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (Agent Intelligence &amp; Evaluations)</t>
+          <t xml:space="preserve"> Software Engineer - 2 Backend</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2537,7 +2545,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>New Delhi, in</t>
+          <t>Gurugram, in</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -2547,7 +2555,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000143976319</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000143738909</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2564,12 +2572,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>Lendingkart</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Software Engineer - 2 Backend</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2584,7 +2592,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Gurugram, in</t>
+          <t>Bengaluru, in</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -2594,12 +2602,12 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000143738909</t>
+          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://careers.smartrecruiters.com/lendingkart</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2611,17 +2619,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Lendingkart</t>
+          <t>Licious</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>By: Licious DevOps</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2629,11 +2637,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
+      <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -2641,12 +2645,12 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
+          <t>https://careers.licious.com/author/adminlic/</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/lendingkart</t>
+          <t>https://www.licious.in/careers</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2658,17 +2662,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Licious</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>By: Licious DevOps</t>
+          <t>Internship Opportunities</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2684,12 +2688,12 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>https://careers.licious.com/author/adminlic/</t>
+          <t>https://careers.linkedin.com/pathways-programs/internships</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>https://www.licious.in/careers</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -2706,12 +2710,12 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Internship Opportunities</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2727,7 +2731,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/pathways-programs/internships</t>
+          <t>https://careers.linkedin.com/Teams/Engineering</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2744,17 +2748,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Automation engineer (Warehouse Automation)</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2762,7 +2766,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -2770,12 +2778,12 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/Teams/Engineering</t>
+          <t>https://jobs.lever.co/meesho/fe839191-1761-4094-9d3c-4d554904b84d</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -2792,12 +2800,12 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Automation engineer (Warehouse Automation)</t>
+          <t>Trainee - Recruitment Coordinator</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -2817,7 +2825,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/fe839191-1761-4094-9d3c-4d554904b84d</t>
+          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2834,12 +2842,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>MoEngage</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>GTM Engineer – Meesho AI Services (MAS)</t>
+          <t>For Developers</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -2852,11 +2860,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
+      <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -2864,12 +2868,12 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/c49e13f6-f027-42f3-98b5-745d83997cbf</t>
+          <t>https://www.moengage.com/role/for-developers/</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://www.moengage.com/careers/</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -2881,17 +2885,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>Mphasis</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Trainee - Recruitment Coordinator</t>
+          <t>TESTING</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -2899,11 +2903,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
+      <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -2911,12 +2911,12 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
+          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://careers.mphasis.com/</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -2928,17 +2928,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>MoEngage</t>
+          <t>PTC India</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>For Developers</t>
+          <t>Learn more about PTC internships</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/role/for-developers/</t>
+          <t>https://www.ptc.com/en/careers/internships</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/careers/</t>
+          <t>https://www.ptc.com/en/careers</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -2971,17 +2971,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Mphasis</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>TESTING</t>
+          <t>Admin &amp; Operations - Internship</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -2989,7 +2989,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Noida, Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -2997,12 +3001,12 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
+          <t>https://jobs.lever.co/paytm/6c1b9af2-9a7c-4cd2-a97b-54e956cf82f1</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -3014,12 +3018,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>PTC India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Learn more about PTC internships</t>
+          <t>Intern-Talent Acquisition</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3032,7 +3036,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -3040,12 +3048,12 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers/internships</t>
+          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -3062,7 +3070,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Operations - Internship</t>
+          <t>Product Management - Intern</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3087,7 +3095,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/6c1b9af2-9a7c-4cd2-a97b-54e956cf82f1</t>
+          <t>https://jobs.lever.co/paytm/1155c0e3-bf03-4b46-97f0-44673b6518f7</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3109,7 +3117,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Intern-Talent Acquisition</t>
+          <t>Product Management - Intern - Telco.</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3124,7 +3132,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -3134,7 +3142,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
+          <t>https://jobs.lever.co/paytm/5648edd6-b73b-4156-96f5-343f4d851610</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3156,7 +3164,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Product Management - Intern</t>
+          <t>Product Management Intern- Insurance</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3166,7 +3174,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>recent graduate</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3181,7 +3189,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/1155c0e3-bf03-4b46-97f0-44673b6518f7</t>
+          <t>https://jobs.lever.co/paytm/4a97658f-ac6f-4a86-b483-ae50dd5c7a46</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3203,7 +3211,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Product Management - Intern - Telco.</t>
+          <t>Talent Acquisition Intern</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3228,7 +3236,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/5648edd6-b73b-4156-96f5-343f4d851610</t>
+          <t>https://jobs.lever.co/paytm/08ee2a10-3268-497e-bc10-7c7fee7caa66</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3245,27 +3253,27 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>PhonePe</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Product Management Intern- Insurance</t>
+          <t>AI Video Specialist</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>recent graduate</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -3275,12 +3283,12 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/4a97658f-ac6f-4a86-b483-ae50dd5c7a46</t>
+          <t>https://job-boards.greenhouse.io/phonepe/jobs/7735150003</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://boards.greenhouse.io/phonepe</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -3292,17 +3300,17 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>PhonePe</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern</t>
+          <t>Firmware Engineer(5-7 years)</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3312,7 +3320,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -3322,12 +3330,12 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/08ee2a10-3268-497e-bc10-7c7fee7caa66</t>
+          <t>https://job-boards.greenhouse.io/phonepe/jobs/7765845003</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://boards.greenhouse.io/phonepe</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -3344,17 +3352,17 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>AI Video Specialist</t>
+          <t>Service Delivery Engineer, SRE</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>1-3 years</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3369,7 +3377,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/phonepe/jobs/7735150003</t>
+          <t>https://job-boards.greenhouse.io/phonepe/jobs/7762335003</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3391,12 +3399,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Firmware Engineer(5-7 years)</t>
+          <t>Site Reliability Engineer - 2</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -3416,7 +3424,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/phonepe/jobs/7765845003</t>
+          <t>https://job-boards.greenhouse.io/phonepe/jobs/7766868003</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3438,17 +3446,17 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Service Delivery Engineer, SRE</t>
+          <t>Software Engineer, Android</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>1-3 years</t>
+          <t>1-2 years</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3463,7 +3471,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/phonepe/jobs/7762335003</t>
+          <t>https://job-boards.greenhouse.io/phonepe/jobs/7799494003</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3480,17 +3488,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>PhonePe</t>
+          <t>Publicis Sapient India</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer - 2</t>
+          <t>Join our engineering talent community</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -3498,11 +3506,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -3510,12 +3514,12 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/phonepe/jobs/7766868003</t>
+          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/phonepe</t>
+          <t>https://careers.publicissapient.com/</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -3527,27 +3531,27 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>PhonePe</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Android</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>1-2 years</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -3557,12 +3561,12 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/phonepe/jobs/7799494003</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/phonepe</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -3574,12 +3578,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Publicis Sapient India</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Join our engineering talent community</t>
+          <t>Laravel Developer</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3592,7 +3596,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr"/>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Indore, in</t>
+        </is>
+      </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -3600,12 +3608,12 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>https://careers.publicissapient.com/</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -3622,7 +3630,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Node.js Developer</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -3647,7 +3655,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -3664,17 +3672,17 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Ramco Systems</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Laravel Developer</t>
+          <t>Internships</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -3682,11 +3690,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>Indore, in</t>
-        </is>
-      </c>
+      <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -3694,12 +3698,12 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
+          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://www.ramco.com/careers/</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -3711,17 +3715,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Razorpay</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Node.js Developer</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -3731,7 +3735,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -3741,12 +3745,12 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
+          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4723067005</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -3758,17 +3762,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Ramco Systems</t>
+          <t>Razorpay</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Internships</t>
+          <t>Full Stack Builder</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -3776,7 +3780,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr"/>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -3784,12 +3792,12 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
+          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4699107005</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/</t>
+          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -3801,12 +3809,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Razorpay</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Payroll Industrial Trainee</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -3821,7 +3829,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -3831,12 +3839,12 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4723067005</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8070886?gh_jid=8070886</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -3848,17 +3856,17 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Razorpay</t>
+          <t>Sarvam AI</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Full Stack Builder</t>
+          <t>Machine Learning Engineer, Vision</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -3878,12 +3886,12 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4699107005</t>
+          <t>https://jobs.ashbyhq.com/sarvam/282019f4-f86b-4fe0-a643-bbac0cd8a751</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
+          <t>https://jobs.ashbyhq.com/sarvam</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -3895,17 +3903,17 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Scaler</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Payroll Industrial Trainee</t>
+          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -3915,7 +3923,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Remote Instructor- Python</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -3925,12 +3933,12 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8070886?gh_jid=8070886</t>
+          <t>https://www.scaler.com/careers/remote-instructor-python</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://www.scaler.com/careers/</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -3942,17 +3950,17 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Sarvam AI</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Vision</t>
+          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -3960,11 +3968,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E77" s="2" t="inlineStr"/>
       <c r="F77" s="2" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -3972,12 +3976,12 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sarvam/282019f4-f86b-4fe0-a643-bbac0cd8a751</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MjksInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sarvam</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -3989,17 +3993,17 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Scaler</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
+          <t>AI Animator</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -4007,11 +4011,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>Remote Instructor- Python</t>
-        </is>
-      </c>
+      <c r="E78" s="2" t="inlineStr"/>
       <c r="F78" s="2" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -4019,12 +4019,12 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/remote-instructor-python</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MTYsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -4041,12 +4041,12 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
+          <t>AI Animator</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MjksInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>AI Animator</t>
+          <t>Intern - Content Moderation(Tamil)</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MTYsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MDUsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>AI Animator</t>
+          <t>Video Editor- AI</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjIzOTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4165,17 +4165,17 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Intern - Content Moderation(Tamil)</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -4183,7 +4183,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr"/>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -4191,12 +4195,12 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MDUsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -4208,17 +4212,17 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Video Editor- AI</t>
+          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -4226,7 +4230,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr"/>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -4234,12 +4242,12 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjIzOTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -4251,17 +4259,17 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>Snowflake India</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>Account Engineer</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -4271,7 +4279,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Gurugram, in</t>
+          <t>CO-Colombia-Remote</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -4281,12 +4289,12 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
+          <t>https://jobs.ashbyhq.com/snowflake/4fafd350-a140-426f-8602-310b8d75b5fd</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://jobs.ashbyhq.com/snowflake</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -4298,17 +4306,17 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>Sprinklr</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
+          <t>Internship and Early Careers</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -4316,11 +4324,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
+      <c r="E85" s="2" t="inlineStr"/>
       <c r="F85" s="2" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -4328,12 +4332,12 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
+          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://www.sprinklr.com/careers/</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
@@ -4345,12 +4349,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Snowflake India</t>
+          <t>Unacademy</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Account Engineer</t>
+          <t>Test Jerin</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -4365,7 +4369,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>CO-Colombia-Remote</t>
+          <t>Bengaluru, in</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -4375,12 +4379,12 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/snowflake/4fafd350-a140-426f-8602-310b8d75b5fd</t>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/snowflake</t>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -4392,17 +4396,17 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Sprinklr</t>
+          <t>Unacademy</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Internship and Early Careers</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -4410,7 +4414,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr"/>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -4418,12 +4426,12 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -4435,12 +4443,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Unacademy</t>
+          <t>upGrad</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Test Jerin</t>
+          <t>Data Science Bootcamp with AI</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -4453,11 +4461,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
+      <c r="E88" s="2" t="inlineStr"/>
       <c r="F88" s="2" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -4465,12 +4469,12 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+          <t>https://www.upgrad.com/bootcamps/job-linked-data-science-advanced-bootcamp/</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
+          <t>https://www.upgrad.com/careers/</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
@@ -4479,98 +4483,8 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>Unacademy</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>Software Engineer, Backend</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G89" s="3" t="inlineStr">
-        <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
-        </is>
-      </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>upGrad</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>Data Science Bootcamp with AI</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr"/>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G90" s="3" t="inlineStr">
-        <is>
-          <t>https://www.upgrad.com/bootcamps/job-linked-data-science-advanced-bootcamp/</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>https://www.upgrad.com/careers/</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I90"/>
+  <autoFilter ref="A1:I88"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -4659,8 +4573,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId85"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId89"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4672,7 +4584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4760,15 +4672,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Tonbo Imaging</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://www.tonboimaging.com/careers/</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.tonboimaging.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Ather Energy</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>https://www.atherenergy.com/careers</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4777,58 +4709,18 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Capillary Technologies</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>https://www.capillarytech.com/careers/</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.capillarytech.com/careers/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Darwinbox</t>
+          <t>Nykaa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://darwinbox.com/careers</t>
+          <t>https://www.nykaa.com/careers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://darwinbox.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Nykaa</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>https://www.nykaa.com/careers</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.nykaa.com/careers
 Call log:
@@ -4837,18 +4729,18 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Juspay</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>https://juspay.io/careers</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4857,38 +4749,38 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MakeMyTrip</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://careers.makemytrip.com/</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://careers.makemytrip.com/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LatentView Analytics</t>
+          <t>FirstCry</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://www.latentview.com/careers/</t>
+          <t>https://www.firstcry.com/careers</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.latentview.com/careers/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>FirstCry</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>https://www.firstcry.com/careers</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4897,38 +4789,18 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>MakeMyTrip</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>https://careers.makemytrip.com/</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://careers.makemytrip.com/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Zomato</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>https://www.zomato.com/careers</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.zomato.com/careers
 Call log:
@@ -4937,18 +4809,18 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Coforge</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>https://www.coforge.com/careers</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.coforge.com/careers
 Call log:
@@ -4957,18 +4829,18 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Persistent Systems</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>https://www.persistent.com/careers/</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.persistent.com/careers/
 Call log:
@@ -4977,18 +4849,18 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Udaan</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>https://udaan.com/careers</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
